--- a/posts/assurance_maladie/data/ofs/indicateur_reduction_primes.xlsx
+++ b/posts/assurance_maladie/data/ofs/indicateur_reduction_primes.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\posts\assurance_maladie\data\ofs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AD7CC6-EAFE-40D2-A0AD-16331AA0E6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="510" windowWidth="28485" windowHeight="14970" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2020-2023" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="2010_2019" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="1996_2009" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="2020-2023" sheetId="1" r:id="rId1"/>
+    <sheet name="2010_2019" sheetId="2" r:id="rId2"/>
+    <sheet name="1996_2009" sheetId="3" r:id="rId3"/>
+    <sheet name="total" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">1996_2009!$A$1:$O$23</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">2010_2019!$A$1:$K$23</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'2020-2023'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'1996_2009'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2010_2019'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2020-2023'!$A$1:$K$23</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="17">
   <si>
-    <t xml:space="preserve">Assurance obligatoire des soins (AOS) : indicateurs de réductions des primes</t>
+    <t>Assurance obligatoire des soins (AOS) : indicateurs de réductions des primes</t>
   </si>
   <si>
-    <t xml:space="preserve">T 13.04.03.03</t>
+    <t>T 13.04.03.03</t>
   </si>
   <si>
     <r>
@@ -52,7 +58,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
   </si>
   <si>
@@ -73,7 +79,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
   </si>
   <si>
@@ -94,7 +100,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
   </si>
   <si>
@@ -115,11 +121,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t>2</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Nombre des ménages</t>
+    <t>Nombre des ménages</t>
   </si>
   <si>
     <r>
@@ -139,7 +145,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
@@ -160,7 +166,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -173,7 +179,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Les données de 1996 et 1997 sont partiellement incomplètes.</t>
+    <t>Les données de 1996 et 1997 sont partiellement incomplètes.</t>
   </si>
   <si>
     <r>
@@ -184,7 +190,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -205,7 +211,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
@@ -218,49 +224,34 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Office fédéral des assurances sociales, Statistique des assurances sociales suisses 2025, tableau  AMal 4.1</t>
+    <t>Office fédéral des assurances sociales, Statistique des assurances sociales suisses 2025, tableau  AMal 4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">© OFAS 2025</t>
+    <t>© OFAS 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Renseignements par téléphone 058 465 03 39 ou par courriel à salome.schuepbach@bsv.admin.ch</t>
+    <t>Renseignements par téléphone 058 465 03 39 ou par courriel à salome.schuepbach@bsv.admin.ch</t>
   </si>
   <si>
-    <t xml:space="preserve">…</t>
+    <t>…</t>
+  </si>
+  <si>
+    <t>annee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,###,##0__;\-#,###,##0__;0__;@__\ "/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,###,##0__;\-#,###,##0__;0__;@__\ "/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -269,7 +260,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -294,6 +285,11 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -310,239 +306,205 @@
     </fill>
   </fills>
   <borders count="8">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -550,12 +512,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -584,7 +546,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -605,7 +567,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -656,7 +618,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -674,28 +636,27 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.43"/>
+    <col min="1" max="1" width="45.265625" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.86328125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -703,224 +664,216 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="7">
         <v>2020</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="7">
         <v>2021</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="7">
         <v>2022</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="n">
-        <v>2371506.66041949</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>2345339.95412828</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>2260584.49093634</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>2452735.57033284</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11">
+        <v>2371506.6604194902</v>
+      </c>
+      <c r="C7" s="11">
+        <v>2345339.9541282798</v>
+      </c>
+      <c r="D7" s="11">
+        <v>2260584.4909363398</v>
+      </c>
+      <c r="E7" s="11">
+        <v>2452735.5703328401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="11" t="n">
-        <v>1265227.38065332</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>1249053.31685337</v>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="B8" s="11">
+        <v>1265227.3806533201</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1249053.3168533701</v>
+      </c>
+      <c r="D8" s="11">
         <v>1205286.59966753</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>1308717.56195283</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="11">
+        <v>1308717.5619528301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="n">
-        <v>1106279.27976617</v>
-      </c>
-      <c r="C9" s="11" t="n">
+      <c r="B9" s="11">
+        <v>1106279.2797661701</v>
+      </c>
+      <c r="C9" s="11">
         <v>1096286.63727491</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="11">
         <v>1055297.89126881</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="11">
         <v>1144018.00838001</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>0.27605180460136</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>0.270987660331904</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>0.257315375270158</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0.27530839632179</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="13">
+        <v>0.27605180460135997</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0.27098766033190402</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0.25731537527015802</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.27530839632178999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="n">
-        <v>1436808.68015117</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>1378238.50771071</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>1351312.75771708</v>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="B11" s="11">
+        <v>1436808.6801511699</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1378238.5077107099</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1351312.7577170799</v>
+      </c>
+      <c r="E11" s="11">
         <v>1439228.27368988</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>3803.27298265281</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>3911.90671172399</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>3961.80866569667</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>4125.75980315926</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="11">
+        <v>3803.2729826528098</v>
+      </c>
+      <c r="C12" s="11">
+        <v>3911.9067117239902</v>
+      </c>
+      <c r="D12" s="11">
+        <v>3961.8086656966698</v>
+      </c>
+      <c r="E12" s="11">
+        <v>4125.7598031592597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="90" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="11.43"/>
+    <col min="1" max="1" width="45.265625" style="1" customWidth="1"/>
+    <col min="2" max="11" width="8.86328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -937,7 +890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -950,7 +903,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -963,40 +916,40 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="7">
         <v>2010</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="7">
         <v>2011</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="7">
         <v>2012</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="7">
         <v>2013</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="7">
         <v>2014</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="7">
         <v>2015</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="7">
         <v>2016</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="7">
         <v>2017</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="7">
         <v>2018</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1009,7 +962,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1022,217 +975,217 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="11">
         <v>2315252</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="11">
         <v>2273693</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>2308013.1256</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="11">
+        <v>2308013.1255999999</v>
+      </c>
+      <c r="E7" s="11">
         <v>2253279</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="11">
         <v>2191164</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="11">
         <v>2222034.23149388</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="11">
         <v>2278684</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="11">
         <v>2217239</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="11">
         <v>2219531.23</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="11">
         <v>2317981</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="11">
         <v>1234301.13044299</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="11">
         <v>1212889.4967387</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>1234516.31066727</v>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="D8" s="11">
+        <v>1234516.3106672701</v>
+      </c>
+      <c r="E8" s="11">
         <v>1205282</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>1178616.85061938</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>1187418.9310642</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>1216806.089</v>
-      </c>
-      <c r="I8" s="11" t="n">
+      <c r="F8" s="11">
+        <v>1178616.8506193799</v>
+      </c>
+      <c r="G8" s="11">
+        <v>1187418.9310641999</v>
+      </c>
+      <c r="H8" s="11">
+        <v>1216806.0889999999</v>
+      </c>
+      <c r="I8" s="11">
         <v>1182515.21</v>
       </c>
-      <c r="J8" s="11" t="n">
-        <v>1185263.035</v>
-      </c>
-      <c r="K8" s="11" t="n">
+      <c r="J8" s="11">
+        <v>1185263.0349999999</v>
+      </c>
+      <c r="K8" s="11">
         <v>1236472.585</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="11">
         <v>1080950.86955701</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="11">
         <v>1060803.5032613</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="11">
         <v>1073496.81493273</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="11">
         <v>1047997</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="11">
         <v>1012547.14938062</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="11">
         <v>1034615.30042968</v>
       </c>
-      <c r="H9" s="11" t="n">
-        <v>1061877.911</v>
-      </c>
-      <c r="I9" s="11" t="n">
+      <c r="H9" s="11">
+        <v>1061877.9110000001</v>
+      </c>
+      <c r="I9" s="11">
         <v>1034723.79</v>
       </c>
-      <c r="J9" s="11" t="n">
-        <v>1034268.195</v>
-      </c>
-      <c r="K9" s="11" t="n">
+      <c r="J9" s="11">
+        <v>1034268.1949999999</v>
+      </c>
+      <c r="K9" s="11">
         <v>1081508.415</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>0.297603122397461</v>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="B10" s="13">
+        <v>0.29760312239746101</v>
+      </c>
+      <c r="C10" s="13">
         <v>0.289171993173439</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="13">
         <v>0.290193541595889</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>0.280052091740536</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0.268647227588371</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.269487532889943</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0.273414815362463</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>0.272</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="13">
+        <v>0.28005209174053602</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.26864722758837101</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.26948753288994298</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.27341481536246298</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="11">
         <v>1270592</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="11">
         <v>1274390</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>1317820.24297065</v>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="D11" s="11">
+        <v>1317820.2429706501</v>
+      </c>
+      <c r="E11" s="11">
         <v>1307345</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="11">
         <v>1285045.09537876</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="11">
         <v>1341923.3549569</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="11">
         <v>1376090</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>1350642.812</v>
-      </c>
-      <c r="J11" s="11" t="n">
+      <c r="I11" s="11">
+        <v>1350642.8119999999</v>
+      </c>
+      <c r="J11" s="11">
         <v>1346881.36</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="11">
         <v>1376650.912</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="11">
         <v>3132.27450749729</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="11">
         <v>3193.95764656032</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>3165.87110632205</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>3187.51944306973</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>3253.70425976374</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>3214.38075930946</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>3275.69846485332</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>3471.84246555632</v>
-      </c>
-      <c r="J12" s="11" t="n">
+      <c r="D12" s="11">
+        <v>3165.8711063220499</v>
+      </c>
+      <c r="E12" s="11">
+        <v>3187.5194430697302</v>
+      </c>
+      <c r="F12" s="11">
+        <v>3253.7042597637401</v>
+      </c>
+      <c r="G12" s="11">
+        <v>3214.3807593094598</v>
+      </c>
+      <c r="H12" s="11">
+        <v>3275.6984648533198</v>
+      </c>
+      <c r="I12" s="11">
+        <v>3471.8424655563199</v>
+      </c>
+      <c r="J12" s="11">
         <v>3666.95876719238</v>
       </c>
-      <c r="K12" s="11" t="n">
-        <v>3773.30384817266</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K12" s="11">
+        <v>3773.3038481726599</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1245,7 +1198,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>8</v>
       </c>
@@ -1254,7 +1207,7 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
@@ -1263,7 +1216,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>10</v>
       </c>
@@ -1272,7 +1225,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
@@ -1281,14 +1234,14 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
@@ -1297,7 +1250,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1306,14 +1259,14 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
         <v>14</v>
       </c>
@@ -1322,37 +1275,29 @@
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="90" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="11.43"/>
+    <col min="1" max="1" width="45.265625" style="1" customWidth="1"/>
+    <col min="2" max="15" width="8.86328125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1372,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1389,7 +1334,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -1406,52 +1351,52 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="21" t="n">
+      <c r="B4" s="21">
         <v>1996</v>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="21">
         <v>1997</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="21">
         <v>1998</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="22">
         <v>1999</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="7">
         <v>2000</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="7">
         <v>2001</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="7">
         <v>2002</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="7">
         <v>2003</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="7">
         <v>2004</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="7">
         <v>2005</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="7">
         <v>2006</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="7">
         <v>2007</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="7">
         <v>2008</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="7">
         <v>2009</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -1468,7 +1413,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1485,54 +1430,54 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="11">
         <v>1651697</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="11">
         <v>1955994</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="11">
         <v>2240522</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="11">
         <v>2334267</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="11">
         <v>2337717</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="11">
         <v>2376421</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="11">
         <v>2433822</v>
       </c>
-      <c r="I7" s="11" t="n">
-        <v>2427518.24</v>
-      </c>
-      <c r="J7" s="11" t="n">
+      <c r="I7" s="11">
+        <v>2427518.2400000002</v>
+      </c>
+      <c r="J7" s="11">
         <v>2361377</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="11">
         <v>2262160</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="11">
         <v>2178397</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="11">
         <v>2271950</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="11">
         <v>2249481</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="11">
         <v>2254890</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1496,7 @@
       <c r="F8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="11">
         <v>1263321</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -1563,23 +1508,23 @@
       <c r="J8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="11">
         <v>1203894</v>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>1149226.18131154</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="11">
+        <v>1149226.1813115401</v>
+      </c>
+      <c r="M8" s="11">
         <v>1215982</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>1202326.73190103</v>
-      </c>
-      <c r="O8" s="11" t="n">
+      <c r="N8" s="11">
+        <v>1202326.7319010301</v>
+      </c>
+      <c r="O8" s="11">
         <v>1206076.23765796</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1543,7 @@
       <c r="F9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="11">
         <v>1113100</v>
       </c>
       <c r="H9" s="11" t="s">
@@ -1610,164 +1555,164 @@
       <c r="J9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="11">
         <v>1058266</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="11">
         <v>1029170.81868846</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="11">
         <v>1055968</v>
       </c>
-      <c r="N9" s="11" t="n">
-        <v>1047154.26809897</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11">
+        <v>1047154.2680989699</v>
+      </c>
+      <c r="O9" s="11">
         <v>1048813.76234204</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="13">
         <v>0.23</v>
       </c>
-      <c r="C10" s="13" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="C10" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D10" s="13">
         <v>0.311</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0.32177297173492</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0.329266408093314</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>0.29129080881841</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.301616073395824</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.29579460935901</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>0.292506722093466</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="13">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.32177297173491998</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0.32926640809331398</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0.29129080881841002</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0.30161607339582402</v>
+      </c>
+      <c r="N10" s="13">
+        <v>0.29579460935900997</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0.29250672209346601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="11">
         <v>756457</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="11">
         <v>988940</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="11">
         <v>1178551</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="11">
         <v>1230090</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="11">
         <v>1242695</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="11">
         <v>1268943</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="11">
         <v>1289405</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="11">
         <v>1287365.05</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="11">
         <v>1245875</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="11">
         <v>1215989</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="11">
         <v>1182675</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="11">
         <v>1225436</v>
       </c>
-      <c r="N11" s="11" t="n">
-        <v>1211669.97450089</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11">
+        <v>1211669.9745008899</v>
+      </c>
+      <c r="O11" s="11">
         <v>1229418</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="11">
         <v>1939.5244786551</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>2016.53433676462</v>
-      </c>
-      <c r="D12" s="11" t="n">
+      <c r="C12" s="11">
+        <v>2016.5343367646201</v>
+      </c>
+      <c r="D12" s="11">
         <v>2075.82951268125</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="11">
         <v>2186.56535456755</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>2048.23094097908</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>2094.02628802082</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>2242.89497869172</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>2381.22046268073</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>2544.23597872981</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>2633.05185244274</v>
-      </c>
-      <c r="L12" s="11" t="n">
+      <c r="F12" s="11">
+        <v>2048.2309409790801</v>
+      </c>
+      <c r="G12" s="11">
+        <v>2094.0262880208202</v>
+      </c>
+      <c r="H12" s="11">
+        <v>2242.8949786917201</v>
+      </c>
+      <c r="I12" s="11">
+        <v>2381.2204626807302</v>
+      </c>
+      <c r="J12" s="11">
+        <v>2544.2359787298101</v>
+      </c>
+      <c r="K12" s="11">
+        <v>2633.0518524427398</v>
+      </c>
+      <c r="L12" s="11">
         <v>2797.67399496903</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>2791.26780998763</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>2804.60356410153</v>
-      </c>
-      <c r="O12" s="11" t="n">
+      <c r="M12" s="11">
+        <v>2791.2678099876298</v>
+      </c>
+      <c r="N12" s="11">
+        <v>2804.6035641015301</v>
+      </c>
+      <c r="O12" s="11">
         <v>2881.37483489749</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:15" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1784,7 +1729,7 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>8</v>
       </c>
@@ -1803,7 +1748,7 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
@@ -1822,7 +1767,7 @@
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>10</v>
       </c>
@@ -1841,7 +1786,7 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
@@ -1860,7 +1805,7 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1877,7 +1822,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
@@ -1896,9 +1841,9 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="str">
-        <f aca="false">2010_2019!A20</f>
+        <f>'2010_2019'!A20</f>
         <v>© OFAS 2025</v>
       </c>
       <c r="B20" s="5"/>
@@ -1916,7 +1861,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1933,9 +1878,9 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="str">
-        <f aca="false">2010_2019!A22</f>
+        <f>'2010_2019'!A22</f>
         <v>Renseignements par téléphone 058 465 03 39 ou par courriel à salome.schuepbach@bsv.admin.ch</v>
       </c>
       <c r="B22" s="5"/>
@@ -1954,12 +1899,510 @@
       <c r="O22" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="90" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F37BFD-5293-477D-83E7-01EF945B4E76}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="21">
+        <v>1996</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1651697</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.23</v>
+      </c>
+      <c r="D2" s="11">
+        <v>756457</v>
+      </c>
+      <c r="E2" s="11">
+        <v>1939.5244786551</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="21">
+        <v>1997</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1955994</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D3" s="11">
+        <v>988940</v>
+      </c>
+      <c r="E3" s="11">
+        <v>2016.5343367646201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="21">
+        <v>1998</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2240522</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.311</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1178551</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2075.82951268125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="22">
+        <v>1999</v>
+      </c>
+      <c r="B5" s="11">
+        <v>2334267</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1230090</v>
+      </c>
+      <c r="E5" s="11">
+        <v>2186.56535456755</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>2000</v>
+      </c>
+      <c r="B6" s="11">
+        <v>2337717</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.32177297173491998</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1242695</v>
+      </c>
+      <c r="E6" s="11">
+        <v>2048.2309409790801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>2001</v>
+      </c>
+      <c r="B7" s="11">
+        <v>2376421</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1268943</v>
+      </c>
+      <c r="E7" s="11">
+        <v>2094.0262880208202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>2002</v>
+      </c>
+      <c r="B8" s="11">
+        <v>2433822</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1289405</v>
+      </c>
+      <c r="E8" s="11">
+        <v>2242.8949786917201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2003</v>
+      </c>
+      <c r="B9" s="11">
+        <v>2427518.2400000002</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0.32926640809331398</v>
+      </c>
+      <c r="D9" s="11">
+        <v>1287365.05</v>
+      </c>
+      <c r="E9" s="11">
+        <v>2381.2204626807302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>2004</v>
+      </c>
+      <c r="B10" s="11">
+        <v>2361377</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="D10" s="11">
+        <v>1245875</v>
+      </c>
+      <c r="E10" s="11">
+        <v>2544.2359787298101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="11">
+        <v>2262160</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1215989</v>
+      </c>
+      <c r="E11" s="11">
+        <v>2633.0518524427398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>2006</v>
+      </c>
+      <c r="B12" s="11">
+        <v>2178397</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0.29129080881841002</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1182675</v>
+      </c>
+      <c r="E12" s="11">
+        <v>2797.67399496903</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>2007</v>
+      </c>
+      <c r="B13" s="11">
+        <v>2271950</v>
+      </c>
+      <c r="C13" s="13">
+        <v>0.30161607339582402</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1225436</v>
+      </c>
+      <c r="E13" s="11">
+        <v>2791.2678099876298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>2008</v>
+      </c>
+      <c r="B14" s="11">
+        <v>2249481</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0.29579460935900997</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1211669.9745008899</v>
+      </c>
+      <c r="E14" s="11">
+        <v>2804.6035641015301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>2009</v>
+      </c>
+      <c r="B15" s="11">
+        <v>2254890</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.29250672209346601</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1229418</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2881.37483489749</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>2010</v>
+      </c>
+      <c r="B16" s="11">
+        <v>2315252</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0.29760312239746101</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1270592</v>
+      </c>
+      <c r="E16" s="11">
+        <v>3132.27450749729</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
+        <v>2011</v>
+      </c>
+      <c r="B17" s="11">
+        <v>2273693</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0.289171993173439</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1274390</v>
+      </c>
+      <c r="E17" s="11">
+        <v>3193.95764656032</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
+        <v>2012</v>
+      </c>
+      <c r="B18" s="11">
+        <v>2308013.1255999999</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0.290193541595889</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1317820.2429706501</v>
+      </c>
+      <c r="E18" s="11">
+        <v>3165.8711063220499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
+        <v>2013</v>
+      </c>
+      <c r="B19" s="11">
+        <v>2253279</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.28005209174053602</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1307345</v>
+      </c>
+      <c r="E19" s="11">
+        <v>3187.5194430697302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
+        <v>2014</v>
+      </c>
+      <c r="B20" s="11">
+        <v>2191164</v>
+      </c>
+      <c r="C20" s="13">
+        <v>0.26864722758837101</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1285045.09537876</v>
+      </c>
+      <c r="E20" s="11">
+        <v>3253.7042597637401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>2015</v>
+      </c>
+      <c r="B21" s="11">
+        <v>2222034.23149388</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0.26948753288994298</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1341923.3549569</v>
+      </c>
+      <c r="E21" s="11">
+        <v>3214.3807593094598</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="7">
+        <v>2016</v>
+      </c>
+      <c r="B22" s="11">
+        <v>2278684</v>
+      </c>
+      <c r="C22" s="13">
+        <v>0.27341481536246298</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1376090</v>
+      </c>
+      <c r="E22" s="11">
+        <v>3275.6984648533198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
+        <v>2017</v>
+      </c>
+      <c r="B23" s="11">
+        <v>2217239</v>
+      </c>
+      <c r="C23" s="13">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1350642.8119999999</v>
+      </c>
+      <c r="E23" s="11">
+        <v>3471.8424655563199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="7">
+        <v>2018</v>
+      </c>
+      <c r="B24" s="11">
+        <v>2219531.23</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1346881.36</v>
+      </c>
+      <c r="E24" s="11">
+        <v>3666.95876719238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B25" s="11">
+        <v>2317981</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D25" s="11">
+        <v>1376650.912</v>
+      </c>
+      <c r="E25" s="11">
+        <v>3773.3038481726599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B26" s="11">
+        <v>2371506.6604194902</v>
+      </c>
+      <c r="C26" s="13">
+        <v>0.27605180460135997</v>
+      </c>
+      <c r="D26" s="11">
+        <v>1436808.6801511699</v>
+      </c>
+      <c r="E26" s="11">
+        <v>3803.2729826528098</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
+        <v>2021</v>
+      </c>
+      <c r="B27" s="11">
+        <v>2345339.9541282798</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0.27098766033190402</v>
+      </c>
+      <c r="D27" s="11">
+        <v>1378238.5077107099</v>
+      </c>
+      <c r="E27" s="11">
+        <v>3911.9067117239902</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B28" s="11">
+        <v>2260584.4909363398</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0.25731537527015802</v>
+      </c>
+      <c r="D28" s="11">
+        <v>1351312.7577170799</v>
+      </c>
+      <c r="E28" s="11">
+        <v>3961.8086656966698</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B29" s="11">
+        <v>2452735.5703328401</v>
+      </c>
+      <c r="C29" s="13">
+        <v>0.27530839632178999</v>
+      </c>
+      <c r="D29" s="11">
+        <v>1439228.27368988</v>
+      </c>
+      <c r="E29" s="11">
+        <v>4125.7598031592597</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>